--- a/Data/miR-205_Targets_240821.xlsx
+++ b/Data/miR-205_Targets_240821.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="39">
   <si>
     <t>Probenname</t>
   </si>
@@ -139,6 +139,9 @@
   <si>
     <t>B</t>
   </si>
+  <si>
+    <t>C</t>
+  </si>
 </sst>
 </file>
 
@@ -202,7 +205,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyProtection="1">
       <protection locked="0"/>
@@ -224,6 +227,15 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -508,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K181"/>
+  <dimension ref="A1:K277"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
@@ -611,7 +623,7 @@
         <v>22.506666666666671</v>
       </c>
       <c r="J3" s="8">
-        <f t="shared" ref="J3:J66" si="1">AVERAGE(F3:H3)</f>
+        <f>AVERAGE(F3:H3)</f>
         <v>22.506666666666671</v>
       </c>
     </row>
@@ -643,7 +655,7 @@
         <v>23.349999999999998</v>
       </c>
       <c r="J4" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J4:J66" si="1">AVERAGE(F4:H4)</f>
         <v>23.349999999999998</v>
       </c>
     </row>
@@ -671,7 +683,7 @@
         <v>22.4</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(E5:H5)</f>
         <v>22.933333333333337</v>
       </c>
       <c r="J5" s="8">
@@ -3781,7 +3793,7 @@
       <c r="D98" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E98" s="9">
+      <c r="F98" s="9">
         <v>31.04</v>
       </c>
       <c r="I98" s="9">
@@ -3804,7 +3816,7 @@
       <c r="D99" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E99" s="9">
+      <c r="F99" s="9">
         <v>24.37</v>
       </c>
       <c r="I99" s="9">
@@ -3827,7 +3839,7 @@
       <c r="D100" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E100" s="9">
+      <c r="F100" s="9">
         <v>25.91</v>
       </c>
       <c r="I100" s="9">
@@ -3850,7 +3862,7 @@
       <c r="D101" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E101" s="9">
+      <c r="F101" s="9">
         <v>24.96</v>
       </c>
       <c r="I101" s="9">
@@ -3873,7 +3885,7 @@
       <c r="D102" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E102" s="9">
+      <c r="F102" s="9">
         <v>25.14</v>
       </c>
       <c r="I102" s="9">
@@ -3896,7 +3908,7 @@
       <c r="D103" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E103" s="9">
+      <c r="F103" s="9">
         <v>31.08</v>
       </c>
       <c r="I103" s="9">
@@ -3919,7 +3931,7 @@
       <c r="D104" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E104" s="9">
+      <c r="F104" s="9">
         <v>25.09</v>
       </c>
       <c r="I104" s="9">
@@ -3942,7 +3954,7 @@
       <c r="D105" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E105" s="9">
+      <c r="F105" s="9">
         <v>30.65</v>
       </c>
       <c r="I105" s="9">
@@ -3965,7 +3977,7 @@
       <c r="D106" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E106" s="9">
+      <c r="F106" s="9">
         <v>26.41</v>
       </c>
       <c r="I106" s="9">
@@ -3988,7 +4000,7 @@
       <c r="D107" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
       <c r="I107" s="9"/>
       <c r="J107" s="9"/>
     </row>
@@ -4005,7 +4017,7 @@
       <c r="D108" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E108" s="9">
+      <c r="F108" s="9">
         <v>21.87</v>
       </c>
       <c r="I108" s="9">
@@ -4028,7 +4040,7 @@
       <c r="D109" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E109" s="9">
+      <c r="F109" s="9">
         <v>24.37</v>
       </c>
       <c r="I109" s="9">
@@ -4051,7 +4063,7 @@
       <c r="D110" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E110" s="9">
+      <c r="F110" s="9">
         <v>32.01</v>
       </c>
       <c r="I110" s="9">
@@ -4074,7 +4086,7 @@
       <c r="D111" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E111" s="9">
+      <c r="F111" s="9">
         <v>25.06</v>
       </c>
       <c r="I111" s="9">
@@ -4097,7 +4109,7 @@
       <c r="D112" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E112" s="9">
+      <c r="F112" s="9">
         <v>27.12</v>
       </c>
       <c r="I112" s="9">
@@ -4120,7 +4132,7 @@
       <c r="D113" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E113" s="9">
+      <c r="F113" s="9">
         <v>25.77</v>
       </c>
       <c r="I113" s="9">
@@ -4143,7 +4155,7 @@
       <c r="D114" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E114" s="9">
+      <c r="F114" s="9">
         <v>25.85</v>
       </c>
       <c r="I114" s="9">
@@ -4166,7 +4178,7 @@
       <c r="D115" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E115" s="9">
+      <c r="F115" s="9">
         <v>32.79</v>
       </c>
       <c r="I115" s="9">
@@ -4189,7 +4201,7 @@
       <c r="D116" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E116" s="9">
+      <c r="F116" s="9">
         <v>26.09</v>
       </c>
       <c r="I116" s="9">
@@ -4212,7 +4224,7 @@
       <c r="D117" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E117" s="9">
+      <c r="F117" s="9">
         <v>32.47</v>
       </c>
       <c r="I117" s="9">
@@ -4235,7 +4247,7 @@
       <c r="D118" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E118" s="9">
+      <c r="F118" s="9">
         <v>27.78</v>
       </c>
       <c r="I118" s="9">
@@ -4258,7 +4270,7 @@
       <c r="D119" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E119" s="9"/>
+      <c r="F119" s="9"/>
       <c r="I119" s="9"/>
       <c r="J119" s="9"/>
     </row>
@@ -4275,7 +4287,7 @@
       <c r="D120" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E120" s="9">
+      <c r="F120" s="9">
         <v>23.21</v>
       </c>
       <c r="I120" s="9">
@@ -4298,7 +4310,7 @@
       <c r="D121" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E121" s="9">
+      <c r="F121" s="9">
         <v>27.13</v>
       </c>
       <c r="I121" s="9">
@@ -4321,7 +4333,7 @@
       <c r="D122" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E122" s="9">
+      <c r="F122" s="9">
         <v>30.04</v>
       </c>
       <c r="I122" s="9">
@@ -4344,7 +4356,7 @@
       <c r="D123" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E123" s="9">
+      <c r="F123" s="9">
         <v>22.78</v>
       </c>
       <c r="I123" s="9">
@@ -4367,7 +4379,7 @@
       <c r="D124" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E124" s="9">
+      <c r="F124" s="9">
         <v>24.24</v>
       </c>
       <c r="I124" s="9">
@@ -4390,7 +4402,7 @@
       <c r="D125" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E125" s="9">
+      <c r="F125" s="9">
         <v>23.41</v>
       </c>
       <c r="I125" s="9">
@@ -4413,7 +4425,7 @@
       <c r="D126" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E126" s="9">
+      <c r="F126" s="9">
         <v>24.16</v>
       </c>
       <c r="I126" s="9">
@@ -4436,7 +4448,7 @@
       <c r="D127" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E127" s="9"/>
+      <c r="F127" s="9"/>
       <c r="I127" s="9"/>
       <c r="J127" s="9"/>
     </row>
@@ -4453,7 +4465,7 @@
       <c r="D128" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E128" s="9">
+      <c r="F128" s="9">
         <v>24.04</v>
       </c>
       <c r="I128" s="9">
@@ -4476,7 +4488,7 @@
       <c r="D129" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E129" s="9">
+      <c r="F129" s="9">
         <v>30.06</v>
       </c>
       <c r="I129" s="9">
@@ -4499,7 +4511,7 @@
       <c r="D130" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E130" s="9">
+      <c r="F130" s="9">
         <v>28.33</v>
       </c>
       <c r="I130" s="9">
@@ -4522,7 +4534,7 @@
       <c r="D131" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
       <c r="I131" s="9"/>
       <c r="J131" s="9"/>
     </row>
@@ -4539,7 +4551,7 @@
       <c r="D132" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E132" s="9">
+      <c r="F132" s="9">
         <v>22.1</v>
       </c>
       <c r="I132" s="9">
@@ -4562,7 +4574,7 @@
       <c r="D133" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E133" s="9">
+      <c r="F133" s="9">
         <v>24.4</v>
       </c>
       <c r="I133" s="9">
@@ -4585,7 +4597,7 @@
       <c r="D134" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E134" s="9">
+      <c r="F134" s="9">
         <v>33.450000000000003</v>
       </c>
       <c r="I134" s="9">
@@ -4608,7 +4620,7 @@
       <c r="D135" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E135" s="9">
+      <c r="F135" s="9">
         <v>25.72</v>
       </c>
       <c r="I135" s="9">
@@ -4631,7 +4643,7 @@
       <c r="D136" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E136" s="9">
+      <c r="F136" s="9">
         <v>26.73</v>
       </c>
       <c r="I136" s="9">
@@ -4654,7 +4666,7 @@
       <c r="D137" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E137" s="9">
+      <c r="F137" s="9">
         <v>26.16</v>
       </c>
       <c r="I137" s="9">
@@ -4677,7 +4689,7 @@
       <c r="D138" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E138" s="9">
+      <c r="F138" s="9">
         <v>26.44</v>
       </c>
       <c r="I138" s="9">
@@ -4700,7 +4712,7 @@
       <c r="D139" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E139" s="9"/>
+      <c r="F139" s="9"/>
       <c r="I139" s="9"/>
       <c r="J139" s="9"/>
     </row>
@@ -4717,7 +4729,7 @@
       <c r="D140" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E140" s="9">
+      <c r="F140" s="9">
         <v>26.61</v>
       </c>
       <c r="I140" s="9">
@@ -4740,7 +4752,7 @@
       <c r="D141" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E141" s="9"/>
+      <c r="F141" s="9"/>
       <c r="I141" s="9"/>
       <c r="J141" s="9"/>
     </row>
@@ -4757,7 +4769,7 @@
       <c r="D142" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E142" s="9">
+      <c r="F142" s="9">
         <v>29.39</v>
       </c>
       <c r="I142" s="9">
@@ -4780,7 +4792,7 @@
       <c r="D143" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E143" s="9"/>
+      <c r="F143" s="9"/>
       <c r="I143" s="9"/>
       <c r="J143" s="9"/>
     </row>
@@ -4797,7 +4809,7 @@
       <c r="D144" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E144" s="9">
+      <c r="F144" s="9">
         <v>23.81</v>
       </c>
       <c r="I144" s="9">
@@ -4820,7 +4832,7 @@
       <c r="D145" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E145" s="9">
+      <c r="F145" s="9">
         <v>27.13</v>
       </c>
       <c r="I145" s="9">
@@ -4843,7 +4855,7 @@
       <c r="D146" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E146" s="9">
+      <c r="F146" s="9">
         <v>32.28</v>
       </c>
       <c r="I146" s="9">
@@ -4866,7 +4878,7 @@
       <c r="D147" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E147" s="9">
+      <c r="F147" s="9">
         <v>23.24</v>
       </c>
       <c r="I147" s="9">
@@ -4889,7 +4901,7 @@
       <c r="D148" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E148" s="9">
+      <c r="F148" s="9">
         <v>24.44</v>
       </c>
       <c r="I148" s="9">
@@ -4912,7 +4924,7 @@
       <c r="D149" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E149" s="9">
+      <c r="F149" s="9">
         <v>23.49</v>
       </c>
       <c r="I149" s="9">
@@ -4935,7 +4947,7 @@
       <c r="D150" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E150" s="9">
+      <c r="F150" s="9">
         <v>23.27</v>
       </c>
       <c r="I150" s="9">
@@ -4958,7 +4970,7 @@
       <c r="D151" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E151" s="9"/>
+      <c r="F151" s="9"/>
       <c r="I151" s="9"/>
       <c r="J151" s="9"/>
     </row>
@@ -4975,7 +4987,7 @@
       <c r="D152" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E152" s="9">
+      <c r="F152" s="9">
         <v>22.23</v>
       </c>
       <c r="I152" s="9">
@@ -4998,7 +5010,7 @@
       <c r="D153" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E153" s="9">
+      <c r="F153" s="9">
         <v>33.1</v>
       </c>
       <c r="I153" s="9">
@@ -5021,7 +5033,7 @@
       <c r="D154" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E154" s="9">
+      <c r="F154" s="9">
         <v>29.66</v>
       </c>
       <c r="I154" s="9">
@@ -5044,7 +5056,7 @@
       <c r="D155" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E155" s="9"/>
+      <c r="F155" s="9"/>
       <c r="I155" s="9"/>
       <c r="J155" s="9"/>
     </row>
@@ -5061,7 +5073,7 @@
       <c r="D156" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E156" s="9">
+      <c r="F156" s="9">
         <v>23.09</v>
       </c>
       <c r="I156" s="9">
@@ -5084,7 +5096,7 @@
       <c r="D157" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E157" s="9">
+      <c r="F157" s="9">
         <v>24.38</v>
       </c>
       <c r="I157" s="9">
@@ -5107,7 +5119,7 @@
       <c r="D158" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E158" s="9">
+      <c r="F158" s="9">
         <v>31.24</v>
       </c>
       <c r="I158" s="9">
@@ -5130,7 +5142,7 @@
       <c r="D159" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E159" s="9">
+      <c r="F159" s="9">
         <v>21.89</v>
       </c>
       <c r="I159" s="9">
@@ -5153,7 +5165,7 @@
       <c r="D160" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E160" s="9">
+      <c r="F160" s="9">
         <v>23.65</v>
       </c>
       <c r="I160" s="9">
@@ -5176,7 +5188,7 @@
       <c r="D161" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E161" s="9">
+      <c r="F161" s="9">
         <v>22.22</v>
       </c>
       <c r="I161" s="9">
@@ -5199,7 +5211,7 @@
       <c r="D162" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E162" s="9">
+      <c r="F162" s="9">
         <v>22.44</v>
       </c>
       <c r="I162" s="9">
@@ -5222,7 +5234,7 @@
       <c r="D163" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E163" s="9">
+      <c r="F163" s="9">
         <v>33.450000000000003</v>
       </c>
       <c r="I163" s="9">
@@ -5245,7 +5257,7 @@
       <c r="D164" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E164" s="9">
+      <c r="F164" s="9">
         <v>20.71</v>
       </c>
       <c r="I164" s="9">
@@ -5268,7 +5280,7 @@
       <c r="D165" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E165" s="9">
+      <c r="F165" s="9">
         <v>32.700000000000003</v>
       </c>
       <c r="I165" s="9">
@@ -5291,7 +5303,7 @@
       <c r="D166" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E166" s="9">
+      <c r="F166" s="9">
         <v>28.07</v>
       </c>
       <c r="I166" s="9">
@@ -5314,7 +5326,7 @@
       <c r="D167" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E167" s="9"/>
+      <c r="F167" s="9"/>
       <c r="I167" s="9"/>
       <c r="J167" s="9"/>
     </row>
@@ -5331,7 +5343,7 @@
       <c r="D168" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E168" s="9">
+      <c r="F168" s="9">
         <v>21.71</v>
       </c>
       <c r="I168" s="9">
@@ -5354,7 +5366,7 @@
       <c r="D169" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E169" s="9">
+      <c r="F169" s="9">
         <v>23.77</v>
       </c>
       <c r="I169" s="9">
@@ -5377,7 +5389,7 @@
       <c r="D170" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E170" s="9">
+      <c r="F170" s="9">
         <v>30.95</v>
       </c>
       <c r="I170" s="9">
@@ -5400,7 +5412,7 @@
       <c r="D171" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E171" s="9">
+      <c r="F171" s="9">
         <v>22.3</v>
       </c>
       <c r="I171" s="9">
@@ -5423,7 +5435,7 @@
       <c r="D172" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E172" s="9">
+      <c r="F172" s="9">
         <v>22.99</v>
       </c>
       <c r="I172" s="9">
@@ -5446,7 +5458,7 @@
       <c r="D173" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E173" s="9">
+      <c r="F173" s="9">
         <v>21.97</v>
       </c>
       <c r="I173" s="9">
@@ -5469,7 +5481,7 @@
       <c r="D174" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E174" s="9">
+      <c r="F174" s="9">
         <v>22.04</v>
       </c>
       <c r="I174" s="9">
@@ -5492,7 +5504,7 @@
       <c r="D175" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E175" s="9">
+      <c r="F175" s="9">
         <v>32.880000000000003</v>
       </c>
       <c r="I175" s="9">
@@ -5515,7 +5527,7 @@
       <c r="D176" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E176" s="9">
+      <c r="F176" s="9">
         <v>21.47</v>
       </c>
       <c r="I176" s="9">
@@ -5538,7 +5550,7 @@
       <c r="D177" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E177" s="9">
+      <c r="F177" s="9">
         <v>32.729999999999997</v>
       </c>
       <c r="I177" s="9">
@@ -5561,7 +5573,7 @@
       <c r="D178" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E178" s="9">
+      <c r="F178" s="9">
         <v>28.97</v>
       </c>
       <c r="I178" s="9">
@@ -5584,7 +5596,7 @@
       <c r="D179" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E179" s="9"/>
+      <c r="F179" s="9"/>
       <c r="I179" s="9"/>
       <c r="J179" s="9"/>
     </row>
@@ -5601,7 +5613,7 @@
       <c r="D180" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E180" s="9">
+      <c r="F180" s="9">
         <v>21.32</v>
       </c>
       <c r="I180" s="9">
@@ -5624,7 +5636,7 @@
       <c r="D181" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E181" s="9">
+      <c r="F181" s="9">
         <v>23.35</v>
       </c>
       <c r="I181" s="9">
@@ -5632,6 +5644,2524 @@
       </c>
       <c r="J181" s="9">
         <v>23.35</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C182" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F182" s="11">
+        <v>27.34</v>
+      </c>
+      <c r="G182" s="12">
+        <v>28.15</v>
+      </c>
+      <c r="I182" s="11">
+        <f>AVERAGE(F182:G182)</f>
+        <v>27.744999999999997</v>
+      </c>
+      <c r="J182" s="11">
+        <v>27.744999999999997</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B183" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C183" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F183" s="11">
+        <v>21.34</v>
+      </c>
+      <c r="G183" s="12">
+        <v>24.34</v>
+      </c>
+      <c r="I183" s="12">
+        <f t="shared" ref="I183:J246" si="4">AVERAGE(F183:G183)</f>
+        <v>22.84</v>
+      </c>
+      <c r="J183" s="11">
+        <v>22.84</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C184" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F184" s="11">
+        <v>23.42</v>
+      </c>
+      <c r="G184" s="12">
+        <v>23.6</v>
+      </c>
+      <c r="I184" s="12">
+        <f t="shared" si="4"/>
+        <v>23.51</v>
+      </c>
+      <c r="J184" s="11">
+        <v>23.51</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C185" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F185" s="11">
+        <v>22.03</v>
+      </c>
+      <c r="G185" s="12">
+        <v>22.47</v>
+      </c>
+      <c r="I185" s="12">
+        <f t="shared" si="4"/>
+        <v>22.25</v>
+      </c>
+      <c r="J185" s="11">
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C186" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F186" s="11">
+        <v>22.7</v>
+      </c>
+      <c r="G186" s="12">
+        <v>22.93</v>
+      </c>
+      <c r="I186" s="12">
+        <f t="shared" si="4"/>
+        <v>22.814999999999998</v>
+      </c>
+      <c r="J186" s="11">
+        <v>22.814999999999998</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C187" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F187" s="11">
+        <v>33.44</v>
+      </c>
+      <c r="G187" s="12">
+        <v>32.58</v>
+      </c>
+      <c r="I187" s="12">
+        <f t="shared" si="4"/>
+        <v>33.01</v>
+      </c>
+      <c r="J187" s="11">
+        <v>33.01</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C188" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F188" s="11">
+        <v>22.34</v>
+      </c>
+      <c r="G188" s="12">
+        <v>22.56</v>
+      </c>
+      <c r="I188" s="12">
+        <f t="shared" si="4"/>
+        <v>22.45</v>
+      </c>
+      <c r="J188" s="11">
+        <v>22.45</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C189" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F189" s="11">
+        <v>28.91</v>
+      </c>
+      <c r="G189" s="12">
+        <v>30.05</v>
+      </c>
+      <c r="I189" s="12">
+        <f t="shared" si="4"/>
+        <v>29.48</v>
+      </c>
+      <c r="J189" s="11">
+        <v>29.48</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C190" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F190" s="11">
+        <v>27.85</v>
+      </c>
+      <c r="G190" s="12">
+        <v>27.11</v>
+      </c>
+      <c r="I190" s="12">
+        <f t="shared" si="4"/>
+        <v>27.48</v>
+      </c>
+      <c r="J190" s="11">
+        <v>27.48</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C191" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F191" s="11"/>
+      <c r="G191" s="12"/>
+      <c r="I191" s="12"/>
+      <c r="J191" s="11"/>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C192" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F192" s="11">
+        <v>20.88</v>
+      </c>
+      <c r="G192" s="12">
+        <v>19.32</v>
+      </c>
+      <c r="I192" s="12">
+        <f t="shared" si="4"/>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J192" s="11">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C193" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F193" s="11">
+        <v>22.04</v>
+      </c>
+      <c r="G193" s="12">
+        <v>23.34</v>
+      </c>
+      <c r="I193" s="12">
+        <f t="shared" si="4"/>
+        <v>22.689999999999998</v>
+      </c>
+      <c r="J193" s="11">
+        <v>22.689999999999998</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C194" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F194" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G194" s="12">
+        <v>27.32</v>
+      </c>
+      <c r="I194" s="12">
+        <f t="shared" si="4"/>
+        <v>27.32</v>
+      </c>
+      <c r="J194" s="11">
+        <v>27.32</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C195" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F195" s="11">
+        <v>21.73</v>
+      </c>
+      <c r="G195" s="12">
+        <v>24.07</v>
+      </c>
+      <c r="I195" s="12">
+        <f t="shared" si="4"/>
+        <v>22.9</v>
+      </c>
+      <c r="J195" s="11">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C196" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F196" s="11">
+        <v>23.37</v>
+      </c>
+      <c r="G196" s="12">
+        <v>23.31</v>
+      </c>
+      <c r="I196" s="12">
+        <f t="shared" si="4"/>
+        <v>23.34</v>
+      </c>
+      <c r="J196" s="11">
+        <v>23.34</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C197" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F197" s="11">
+        <v>23.42</v>
+      </c>
+      <c r="G197" s="12">
+        <v>22.07</v>
+      </c>
+      <c r="I197" s="12">
+        <f t="shared" si="4"/>
+        <v>22.745000000000001</v>
+      </c>
+      <c r="J197" s="11">
+        <v>22.745000000000001</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C198" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F198" s="11">
+        <v>23.93</v>
+      </c>
+      <c r="G198" s="12">
+        <v>22.3</v>
+      </c>
+      <c r="I198" s="12">
+        <f t="shared" si="4"/>
+        <v>23.115000000000002</v>
+      </c>
+      <c r="J198" s="11">
+        <v>23.115000000000002</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C199" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F199" s="11">
+        <v>36.630000000000003</v>
+      </c>
+      <c r="G199" s="12">
+        <v>32.54</v>
+      </c>
+      <c r="I199" s="12">
+        <f t="shared" si="4"/>
+        <v>34.585000000000001</v>
+      </c>
+      <c r="J199" s="11">
+        <v>34.585000000000001</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C200" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F200" s="11">
+        <v>24</v>
+      </c>
+      <c r="G200" s="12">
+        <v>22.21</v>
+      </c>
+      <c r="I200" s="12">
+        <f t="shared" si="4"/>
+        <v>23.105</v>
+      </c>
+      <c r="J200" s="11">
+        <v>23.105</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A201" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C201" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F201" s="11">
+        <v>30.1</v>
+      </c>
+      <c r="G201" s="12">
+        <v>28.95</v>
+      </c>
+      <c r="I201" s="12">
+        <f t="shared" si="4"/>
+        <v>29.524999999999999</v>
+      </c>
+      <c r="J201" s="11">
+        <v>29.524999999999999</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A202" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C202" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F202" s="11">
+        <v>27.78</v>
+      </c>
+      <c r="G202" s="12">
+        <v>27.21</v>
+      </c>
+      <c r="I202" s="12">
+        <f t="shared" si="4"/>
+        <v>27.495000000000001</v>
+      </c>
+      <c r="J202" s="11">
+        <v>27.495000000000001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A203" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C203" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F203" s="11"/>
+      <c r="G203" s="12"/>
+      <c r="I203" s="12"/>
+      <c r="J203" s="11"/>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A204" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C204" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F204" s="11">
+        <v>21.39</v>
+      </c>
+      <c r="G204" s="12">
+        <v>19.88</v>
+      </c>
+      <c r="I204" s="12">
+        <f t="shared" si="4"/>
+        <v>20.634999999999998</v>
+      </c>
+      <c r="J204" s="11">
+        <v>20.634999999999998</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A205" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C205" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F205" s="11">
+        <v>22.78</v>
+      </c>
+      <c r="G205" s="12">
+        <v>22.8</v>
+      </c>
+      <c r="I205" s="12">
+        <f t="shared" si="4"/>
+        <v>22.79</v>
+      </c>
+      <c r="J205" s="11">
+        <v>22.79</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A206" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C206" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F206" s="11">
+        <v>27.52</v>
+      </c>
+      <c r="G206" s="12">
+        <v>27.82</v>
+      </c>
+      <c r="I206" s="12">
+        <f t="shared" si="4"/>
+        <v>27.67</v>
+      </c>
+      <c r="J206" s="11">
+        <v>27.67</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A207" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C207" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F207" s="11">
+        <v>20.92</v>
+      </c>
+      <c r="G207" s="12">
+        <v>23.62</v>
+      </c>
+      <c r="I207" s="12">
+        <f t="shared" si="4"/>
+        <v>22.270000000000003</v>
+      </c>
+      <c r="J207" s="11">
+        <v>22.270000000000003</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A208" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C208" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F208" s="11">
+        <v>22.88</v>
+      </c>
+      <c r="G208" s="12">
+        <v>23.27</v>
+      </c>
+      <c r="I208" s="12">
+        <f t="shared" si="4"/>
+        <v>23.074999999999999</v>
+      </c>
+      <c r="J208" s="11">
+        <v>23.074999999999999</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A209" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C209" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F209" s="11">
+        <v>22.24</v>
+      </c>
+      <c r="G209" s="12">
+        <v>21.88</v>
+      </c>
+      <c r="I209" s="12">
+        <f t="shared" si="4"/>
+        <v>22.06</v>
+      </c>
+      <c r="J209" s="11">
+        <v>22.06</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A210" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C210" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F210" s="11">
+        <v>22.25</v>
+      </c>
+      <c r="G210" s="12">
+        <v>22.49</v>
+      </c>
+      <c r="I210" s="12">
+        <f t="shared" si="4"/>
+        <v>22.369999999999997</v>
+      </c>
+      <c r="J210" s="11">
+        <v>22.369999999999997</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A211" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C211" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F211" s="11">
+        <v>33.11</v>
+      </c>
+      <c r="G211" s="12">
+        <v>31.95</v>
+      </c>
+      <c r="I211" s="12">
+        <f t="shared" si="4"/>
+        <v>32.53</v>
+      </c>
+      <c r="J211" s="11">
+        <v>32.53</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A212" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C212" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F212" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="G212" s="12">
+        <v>22.31</v>
+      </c>
+      <c r="I212" s="12">
+        <f t="shared" si="4"/>
+        <v>22.405000000000001</v>
+      </c>
+      <c r="J212" s="11">
+        <v>22.405000000000001</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A213" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C213" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F213" s="11">
+        <v>28.18</v>
+      </c>
+      <c r="G213" s="12">
+        <v>29.38</v>
+      </c>
+      <c r="I213" s="12">
+        <f t="shared" si="4"/>
+        <v>28.78</v>
+      </c>
+      <c r="J213" s="11">
+        <v>28.78</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A214" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F214" s="11">
+        <v>27.99</v>
+      </c>
+      <c r="G214" s="12">
+        <v>27.48</v>
+      </c>
+      <c r="I214" s="12">
+        <f t="shared" si="4"/>
+        <v>27.734999999999999</v>
+      </c>
+      <c r="J214" s="11">
+        <v>27.734999999999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A215" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C215" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F215" s="11"/>
+      <c r="G215" s="12"/>
+      <c r="I215" s="12"/>
+      <c r="J215" s="11"/>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A216" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C216" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F216" s="11">
+        <v>21.26</v>
+      </c>
+      <c r="G216" s="12">
+        <v>20.11</v>
+      </c>
+      <c r="I216" s="12">
+        <f t="shared" si="4"/>
+        <v>20.685000000000002</v>
+      </c>
+      <c r="J216" s="11">
+        <v>20.685000000000002</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A217" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C217" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F217" s="11">
+        <v>20.45</v>
+      </c>
+      <c r="G217" s="12">
+        <v>22.94</v>
+      </c>
+      <c r="I217" s="12">
+        <f t="shared" si="4"/>
+        <v>21.695</v>
+      </c>
+      <c r="J217" s="11">
+        <v>21.695</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A218" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C218" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F218" s="11">
+        <v>27.41</v>
+      </c>
+      <c r="G218" s="12">
+        <v>27.32</v>
+      </c>
+      <c r="I218" s="12">
+        <f t="shared" si="4"/>
+        <v>27.365000000000002</v>
+      </c>
+      <c r="J218" s="11">
+        <v>27.365000000000002</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A219" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C219" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F219" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="G219" s="12">
+        <v>24.34</v>
+      </c>
+      <c r="I219" s="12">
+        <f t="shared" si="4"/>
+        <v>22.895</v>
+      </c>
+      <c r="J219" s="11">
+        <v>22.895</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A220" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C220" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F220" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="G220" s="12">
+        <v>23.15</v>
+      </c>
+      <c r="I220" s="12">
+        <f t="shared" si="4"/>
+        <v>23.225000000000001</v>
+      </c>
+      <c r="J220" s="11">
+        <v>23.225000000000001</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A221" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F221" s="11">
+        <v>22.26</v>
+      </c>
+      <c r="G221" s="12">
+        <v>22.2</v>
+      </c>
+      <c r="I221" s="12">
+        <f t="shared" si="4"/>
+        <v>22.23</v>
+      </c>
+      <c r="J221" s="11">
+        <v>22.23</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A222" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C222" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F222" s="11">
+        <v>22.77</v>
+      </c>
+      <c r="G222" s="12">
+        <v>22.51</v>
+      </c>
+      <c r="I222" s="12">
+        <f t="shared" si="4"/>
+        <v>22.64</v>
+      </c>
+      <c r="J222" s="11">
+        <v>22.64</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A223" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B223" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C223" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F223" s="11">
+        <v>33.85</v>
+      </c>
+      <c r="G223" s="12">
+        <v>31.65</v>
+      </c>
+      <c r="I223" s="12">
+        <f t="shared" si="4"/>
+        <v>32.75</v>
+      </c>
+      <c r="J223" s="11">
+        <v>32.75</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A224" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C224" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F224" s="11">
+        <v>22.73</v>
+      </c>
+      <c r="G224" s="12">
+        <v>22.33</v>
+      </c>
+      <c r="I224" s="12">
+        <f t="shared" si="4"/>
+        <v>22.53</v>
+      </c>
+      <c r="J224" s="11">
+        <v>22.53</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A225" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B225" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C225" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F225" s="11">
+        <v>28.51</v>
+      </c>
+      <c r="G225" s="12">
+        <v>29.58</v>
+      </c>
+      <c r="I225" s="12">
+        <f t="shared" si="4"/>
+        <v>29.045000000000002</v>
+      </c>
+      <c r="J225" s="11">
+        <v>29.045000000000002</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A226" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C226" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F226" s="11">
+        <v>28.63</v>
+      </c>
+      <c r="G226" s="12">
+        <v>26.66</v>
+      </c>
+      <c r="I226" s="12">
+        <f t="shared" si="4"/>
+        <v>27.645</v>
+      </c>
+      <c r="J226" s="11">
+        <v>27.645</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A227" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B227" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C227" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F227" s="11"/>
+      <c r="G227" s="12"/>
+      <c r="I227" s="12"/>
+      <c r="J227" s="11"/>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A228" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C228" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F228" s="11">
+        <v>20.95</v>
+      </c>
+      <c r="G228" s="12">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="I228" s="12">
+        <f t="shared" si="4"/>
+        <v>20.48</v>
+      </c>
+      <c r="J228" s="11">
+        <v>20.48</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A229" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C229" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F229" s="11">
+        <v>21.87</v>
+      </c>
+      <c r="G229" s="12">
+        <v>22.99</v>
+      </c>
+      <c r="I229" s="12">
+        <f t="shared" si="4"/>
+        <v>22.43</v>
+      </c>
+      <c r="J229" s="11">
+        <v>22.43</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A230" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C230" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F230" s="11">
+        <v>28.1</v>
+      </c>
+      <c r="G230" s="12">
+        <v>28.73</v>
+      </c>
+      <c r="I230" s="12">
+        <f t="shared" si="4"/>
+        <v>28.414999999999999</v>
+      </c>
+      <c r="J230" s="11">
+        <v>28.414999999999999</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A231" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B231" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C231" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F231" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="G231" s="12">
+        <v>23.62</v>
+      </c>
+      <c r="I231" s="12">
+        <f t="shared" si="4"/>
+        <v>22.435000000000002</v>
+      </c>
+      <c r="J231" s="11">
+        <v>22.435000000000002</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A232" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C232" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F232" s="11">
+        <v>22.28</v>
+      </c>
+      <c r="G232" s="12">
+        <v>22.32</v>
+      </c>
+      <c r="I232" s="12">
+        <f t="shared" si="4"/>
+        <v>22.3</v>
+      </c>
+      <c r="J232" s="11">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A233" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C233" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F233" s="11">
+        <v>21.81</v>
+      </c>
+      <c r="G233" s="12">
+        <v>22.1</v>
+      </c>
+      <c r="I233" s="12">
+        <f t="shared" si="4"/>
+        <v>21.954999999999998</v>
+      </c>
+      <c r="J233" s="11">
+        <v>21.954999999999998</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A234" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C234" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F234" s="11">
+        <v>23.47</v>
+      </c>
+      <c r="G234" s="12">
+        <v>23.14</v>
+      </c>
+      <c r="I234" s="12">
+        <f t="shared" si="4"/>
+        <v>23.305</v>
+      </c>
+      <c r="J234" s="11">
+        <v>23.305</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A235" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B235" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C235" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F235" s="11">
+        <v>30.39</v>
+      </c>
+      <c r="G235" s="12">
+        <v>29.43</v>
+      </c>
+      <c r="I235" s="12">
+        <f t="shared" si="4"/>
+        <v>29.91</v>
+      </c>
+      <c r="J235" s="11">
+        <v>29.91</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A236" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C236" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F236" s="11">
+        <v>22.32</v>
+      </c>
+      <c r="G236" s="12">
+        <v>21.7</v>
+      </c>
+      <c r="I236" s="12">
+        <f t="shared" si="4"/>
+        <v>22.009999999999998</v>
+      </c>
+      <c r="J236" s="11">
+        <v>22.009999999999998</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A237" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C237" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F237" s="11">
+        <v>30.88</v>
+      </c>
+      <c r="G237" s="12"/>
+      <c r="I237" s="12">
+        <f t="shared" si="4"/>
+        <v>30.88</v>
+      </c>
+      <c r="J237" s="11">
+        <v>30.88</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A238" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C238" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F238" s="11">
+        <v>25.06</v>
+      </c>
+      <c r="G238" s="12">
+        <v>27.31</v>
+      </c>
+      <c r="I238" s="12">
+        <f t="shared" si="4"/>
+        <v>26.184999999999999</v>
+      </c>
+      <c r="J238" s="11">
+        <v>26.184999999999999</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A239" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C239" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F239" s="11"/>
+      <c r="G239" s="12"/>
+      <c r="I239" s="12"/>
+      <c r="J239" s="11"/>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A240" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C240" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F240" s="11">
+        <v>21.22</v>
+      </c>
+      <c r="G240" s="12">
+        <v>19.86</v>
+      </c>
+      <c r="I240" s="12">
+        <f t="shared" si="4"/>
+        <v>20.54</v>
+      </c>
+      <c r="J240" s="11">
+        <v>20.54</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A241" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B241" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C241" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F241" s="11">
+        <v>22.48</v>
+      </c>
+      <c r="G241" s="12">
+        <v>22.81</v>
+      </c>
+      <c r="I241" s="12">
+        <f t="shared" si="4"/>
+        <v>22.645</v>
+      </c>
+      <c r="J241" s="11">
+        <v>22.645</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A242" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C242" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F242" s="11">
+        <v>28.44</v>
+      </c>
+      <c r="G242" s="12">
+        <v>28.98</v>
+      </c>
+      <c r="I242" s="12">
+        <f t="shared" si="4"/>
+        <v>28.71</v>
+      </c>
+      <c r="J242" s="11">
+        <v>28.71</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A243" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B243" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C243" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F243" s="11">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="G243" s="12">
+        <v>23.03</v>
+      </c>
+      <c r="I243" s="12">
+        <f t="shared" si="4"/>
+        <v>21.59</v>
+      </c>
+      <c r="J243" s="11">
+        <v>21.59</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A244" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C244" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D244" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F244" s="11">
+        <v>21.95</v>
+      </c>
+      <c r="G244" s="12">
+        <v>21.74</v>
+      </c>
+      <c r="I244" s="12">
+        <f t="shared" si="4"/>
+        <v>21.844999999999999</v>
+      </c>
+      <c r="J244" s="11">
+        <v>21.844999999999999</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A245" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B245" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C245" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F245" s="11">
+        <v>22.03</v>
+      </c>
+      <c r="G245" s="12">
+        <v>22.15</v>
+      </c>
+      <c r="I245" s="12">
+        <f t="shared" si="4"/>
+        <v>22.09</v>
+      </c>
+      <c r="J245" s="11">
+        <v>22.09</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A246" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C246" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F246" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="G246" s="12">
+        <v>23.05</v>
+      </c>
+      <c r="I246" s="12">
+        <f t="shared" si="4"/>
+        <v>22.675000000000001</v>
+      </c>
+      <c r="J246" s="11">
+        <v>22.675000000000001</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A247" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B247" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C247" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F247" s="11">
+        <v>29.14</v>
+      </c>
+      <c r="G247" s="12">
+        <v>29.66</v>
+      </c>
+      <c r="I247" s="12">
+        <f t="shared" ref="I247:J277" si="5">AVERAGE(F247:G247)</f>
+        <v>29.4</v>
+      </c>
+      <c r="J247" s="11">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A248" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C248" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F248" s="11">
+        <v>21.56</v>
+      </c>
+      <c r="G248" s="12">
+        <v>21.33</v>
+      </c>
+      <c r="I248" s="12">
+        <f t="shared" si="5"/>
+        <v>21.445</v>
+      </c>
+      <c r="J248" s="11">
+        <v>21.445</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A249" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B249" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C249" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F249" s="11">
+        <v>30.59</v>
+      </c>
+      <c r="G249" s="12">
+        <v>31.19</v>
+      </c>
+      <c r="I249" s="12">
+        <f t="shared" si="5"/>
+        <v>30.89</v>
+      </c>
+      <c r="J249" s="11">
+        <v>30.89</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A250" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C250" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F250" s="11">
+        <v>27.3</v>
+      </c>
+      <c r="G250" s="12">
+        <v>26.87</v>
+      </c>
+      <c r="I250" s="12">
+        <f t="shared" si="5"/>
+        <v>27.085000000000001</v>
+      </c>
+      <c r="J250" s="11">
+        <v>27.085000000000001</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A251" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B251" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C251" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F251" s="11"/>
+      <c r="G251" s="12"/>
+      <c r="I251" s="12"/>
+      <c r="J251" s="11"/>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A252" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C252" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D252" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F252" s="11">
+        <v>21.42</v>
+      </c>
+      <c r="G252" s="12">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="I252" s="12">
+        <f t="shared" si="5"/>
+        <v>20.785</v>
+      </c>
+      <c r="J252" s="11">
+        <v>20.785</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A253" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C253" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D253" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F253" s="11">
+        <v>22.42</v>
+      </c>
+      <c r="G253" s="12">
+        <v>22.86</v>
+      </c>
+      <c r="I253" s="12">
+        <f t="shared" si="5"/>
+        <v>22.64</v>
+      </c>
+      <c r="J253" s="11">
+        <v>22.64</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A254" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C254" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F254" s="11">
+        <v>27.86</v>
+      </c>
+      <c r="G254" s="12">
+        <v>27.57</v>
+      </c>
+      <c r="I254" s="12">
+        <f t="shared" si="5"/>
+        <v>27.715</v>
+      </c>
+      <c r="J254" s="11">
+        <v>27.715</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A255" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B255" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F255" s="11">
+        <v>19.38</v>
+      </c>
+      <c r="G255" s="12">
+        <v>22.39</v>
+      </c>
+      <c r="I255" s="12">
+        <f t="shared" si="5"/>
+        <v>20.884999999999998</v>
+      </c>
+      <c r="J255" s="11">
+        <v>20.884999999999998</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A256" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C256" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D256" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F256" s="11">
+        <v>21.75</v>
+      </c>
+      <c r="G256" s="12">
+        <v>21.66</v>
+      </c>
+      <c r="I256" s="12">
+        <f t="shared" si="5"/>
+        <v>21.704999999999998</v>
+      </c>
+      <c r="J256" s="11">
+        <v>21.704999999999998</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A257" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B257" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C257" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F257" s="11">
+        <v>21.62</v>
+      </c>
+      <c r="G257" s="12">
+        <v>21.63</v>
+      </c>
+      <c r="I257" s="12">
+        <f t="shared" si="5"/>
+        <v>21.625</v>
+      </c>
+      <c r="J257" s="11">
+        <v>21.625</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A258" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C258" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D258" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F258" s="11">
+        <v>22.37</v>
+      </c>
+      <c r="G258" s="12">
+        <v>22.34</v>
+      </c>
+      <c r="I258" s="12">
+        <f t="shared" si="5"/>
+        <v>22.355</v>
+      </c>
+      <c r="J258" s="11">
+        <v>22.355</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A259" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B259" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C259" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F259" s="11">
+        <v>29.46</v>
+      </c>
+      <c r="G259" s="12">
+        <v>29.83</v>
+      </c>
+      <c r="I259" s="12">
+        <f t="shared" si="5"/>
+        <v>29.645</v>
+      </c>
+      <c r="J259" s="11">
+        <v>29.645</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A260" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C260" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D260" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F260" s="11">
+        <v>21.37</v>
+      </c>
+      <c r="G260" s="12">
+        <v>21.28</v>
+      </c>
+      <c r="I260" s="12">
+        <f t="shared" si="5"/>
+        <v>21.325000000000003</v>
+      </c>
+      <c r="J260" s="11">
+        <v>21.325000000000003</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A261" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C261" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F261" s="11">
+        <v>30.31</v>
+      </c>
+      <c r="G261" s="12">
+        <v>30.95</v>
+      </c>
+      <c r="I261" s="12">
+        <f t="shared" si="5"/>
+        <v>30.63</v>
+      </c>
+      <c r="J261" s="11">
+        <v>30.63</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A262" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C262" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F262" s="11">
+        <v>23.74</v>
+      </c>
+      <c r="G262" s="12">
+        <v>27.25</v>
+      </c>
+      <c r="I262" s="12">
+        <f t="shared" si="5"/>
+        <v>25.494999999999997</v>
+      </c>
+      <c r="J262" s="11">
+        <v>25.494999999999997</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A263" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B263" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C263" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F263" s="11"/>
+      <c r="G263" s="12"/>
+      <c r="I263" s="12"/>
+      <c r="J263" s="11"/>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A264" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C264" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D264" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F264" s="11">
+        <v>20.86</v>
+      </c>
+      <c r="G264" s="12">
+        <v>20.14</v>
+      </c>
+      <c r="I264" s="12">
+        <f t="shared" si="5"/>
+        <v>20.5</v>
+      </c>
+      <c r="J264" s="11">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A265" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B265" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C265" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D265" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F265" s="11">
+        <v>22.2</v>
+      </c>
+      <c r="G265" s="12">
+        <v>22.27</v>
+      </c>
+      <c r="I265" s="12">
+        <f t="shared" si="5"/>
+        <v>22.234999999999999</v>
+      </c>
+      <c r="J265" s="11">
+        <v>22.234999999999999</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A266" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B266" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C266" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F266" s="11">
+        <v>28.04</v>
+      </c>
+      <c r="G266" s="12">
+        <v>28.07</v>
+      </c>
+      <c r="I266" s="12">
+        <f t="shared" si="5"/>
+        <v>28.055</v>
+      </c>
+      <c r="J266" s="11">
+        <v>28.055</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A267" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B267" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C267" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D267" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F267" s="11">
+        <v>20.2</v>
+      </c>
+      <c r="G267" s="12">
+        <v>21.9</v>
+      </c>
+      <c r="I267" s="12">
+        <f t="shared" si="5"/>
+        <v>21.049999999999997</v>
+      </c>
+      <c r="J267" s="11">
+        <v>21.049999999999997</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A268" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B268" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C268" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D268" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F268" s="11">
+        <v>21.84</v>
+      </c>
+      <c r="G268" s="12">
+        <v>22.62</v>
+      </c>
+      <c r="I268" s="12">
+        <f t="shared" si="5"/>
+        <v>22.23</v>
+      </c>
+      <c r="J268" s="11">
+        <v>22.23</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A269" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B269" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C269" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D269" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F269" s="11">
+        <v>21.88</v>
+      </c>
+      <c r="G269" s="12">
+        <v>22.25</v>
+      </c>
+      <c r="I269" s="12">
+        <f t="shared" si="5"/>
+        <v>22.064999999999998</v>
+      </c>
+      <c r="J269" s="11">
+        <v>22.064999999999998</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A270" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B270" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C270" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D270" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F270" s="11">
+        <v>22.49</v>
+      </c>
+      <c r="G270" s="12">
+        <v>23.03</v>
+      </c>
+      <c r="I270" s="12">
+        <f t="shared" si="5"/>
+        <v>22.759999999999998</v>
+      </c>
+      <c r="J270" s="11">
+        <v>22.759999999999998</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A271" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B271" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C271" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D271" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F271" s="11">
+        <v>29.16</v>
+      </c>
+      <c r="G271" s="12">
+        <v>30.22</v>
+      </c>
+      <c r="I271" s="12">
+        <f t="shared" si="5"/>
+        <v>29.689999999999998</v>
+      </c>
+      <c r="J271" s="11">
+        <v>29.689999999999998</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A272" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B272" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C272" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F272" s="11">
+        <v>22.06</v>
+      </c>
+      <c r="G272" s="12">
+        <v>22.16</v>
+      </c>
+      <c r="I272" s="12">
+        <f t="shared" si="5"/>
+        <v>22.11</v>
+      </c>
+      <c r="J272" s="11">
+        <v>22.11</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A273" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B273" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C273" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F273" s="11">
+        <v>30.82</v>
+      </c>
+      <c r="G273" s="12">
+        <v>30.63</v>
+      </c>
+      <c r="I273" s="12">
+        <f t="shared" si="5"/>
+        <v>30.725000000000001</v>
+      </c>
+      <c r="J273" s="11">
+        <v>30.725000000000001</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A274" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B274" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C274" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F274" s="11">
+        <v>27.05</v>
+      </c>
+      <c r="G274" s="12">
+        <v>27.08</v>
+      </c>
+      <c r="I274" s="12">
+        <f t="shared" si="5"/>
+        <v>27.064999999999998</v>
+      </c>
+      <c r="J274" s="11">
+        <v>27.064999999999998</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A275" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B275" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C275" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F275" s="11"/>
+      <c r="G275" s="12"/>
+      <c r="I275" s="12"/>
+      <c r="J275" s="11"/>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A276" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B276" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C276" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F276" s="11">
+        <v>20.91</v>
+      </c>
+      <c r="G276" s="12">
+        <v>20.170000000000002</v>
+      </c>
+      <c r="I276" s="12">
+        <f t="shared" si="5"/>
+        <v>20.54</v>
+      </c>
+      <c r="J276" s="11">
+        <v>20.54</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A277" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B277" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C277" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F277" s="11">
+        <v>21.98</v>
+      </c>
+      <c r="G277" s="12">
+        <v>23.2</v>
+      </c>
+      <c r="I277" s="12">
+        <f t="shared" si="5"/>
+        <v>22.59</v>
+      </c>
+      <c r="J277" s="11">
+        <v>22.59</v>
       </c>
     </row>
   </sheetData>
